--- a/jpcore-r4/feature/ImagingStudyTest/StructureDefinition-jp-medicationrequest-dispenserequest-instructionfordispense.xlsx
+++ b/jpcore-r4/feature/ImagingStudyTest/StructureDefinition-jp-medicationrequest-dispenserequest-instructionfordispense.xlsx
@@ -269,7 +269,7 @@
 </t>
   </si>
   <si>
-    <t>ele-1:すべてのFHIR要素には、@valueまたは子供が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+    <t>ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 ext-1:両方ではなく、拡張または値[x]が必要です / Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
   </si>
   <si>
@@ -347,7 +347,7 @@
     <t>薬剤単位の調剤・払い出し指示</t>
   </si>
   <si>
-    <t xml:space="preserve">ele-1:すべてのFHIR要素には、@valueまたは子供が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+    <t xml:space="preserve">ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 </t>
   </si>
   <si>
